--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/Dropbox (Personal)/School/Teaching/DAV5300 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15CAEC9C-008C-C14A-B68F-760B36E32632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46572682-9DD6-F040-A731-9D1A1A4D57FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1480" yWindow="4680" windowWidth="25340" windowHeight="14540" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>Date</t>
   </si>
@@ -193,6 +193,9 @@
   </si>
   <si>
     <t>/slides/02-Summarizing_Data.html</t>
+  </si>
+  <si>
+    <t>/slides/03-Summarizing_Data.html</t>
   </si>
 </sst>
 </file>
@@ -644,6 +647,9 @@
       <c r="C4" t="s">
         <v>10</v>
       </c>
+      <c r="D4" t="s">
+        <v>53</v>
+      </c>
       <c r="E4" t="s">
         <v>29</v>
       </c>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/Dropbox (Personal)/School/Teaching/DAV5300 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46572682-9DD6-F040-A731-9D1A1A4D57FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C42ECABA-D2A9-B045-BEEE-AB704D96DEAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1480" yWindow="4680" windowWidth="25340" windowHeight="14540" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -195,7 +195,7 @@
     <t>/slides/02-Summarizing_Data.html</t>
   </si>
   <si>
-    <t>/slides/03-Summarizing_Data.html</t>
+    <t>/slides/03-Probability_and_Distributions.html</t>
   </si>
 </sst>
 </file>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/Dropbox (Personal)/School/Teaching/DAV5300 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C42ECABA-D2A9-B045-BEEE-AB704D96DEAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65F0C993-17CE-3641-85EC-45A73CC67FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1480" yWindow="4680" windowWidth="25340" windowHeight="14540" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>Date</t>
   </si>
@@ -196,6 +196,9 @@
   </si>
   <si>
     <t>/slides/03-Probability_and_Distributions.html</t>
+  </si>
+  <si>
+    <t>/slides/05-Foundation_for_Inference.html</t>
   </si>
 </sst>
 </file>
@@ -668,6 +671,9 @@
       <c r="C5" t="s">
         <v>11</v>
       </c>
+      <c r="D5" t="s">
+        <v>54</v>
+      </c>
       <c r="E5" t="s">
         <v>31</v>
       </c>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/Dropbox (Personal)/School/Teaching/DAV5300 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65F0C993-17CE-3641-85EC-45A73CC67FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE0192D-3EDE-BF42-B04A-C7D1ECA7577B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1480" yWindow="4680" windowWidth="25340" windowHeight="14540" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t>Date</t>
   </si>
@@ -199,6 +199,12 @@
   </si>
   <si>
     <t>/slides/05-Foundation_for_Inference.html</t>
+  </si>
+  <si>
+    <t>/slides/06-Inference_for_Categorical_Data.html</t>
+  </si>
+  <si>
+    <t>/slides/07-Inference_for_Numerical_Data.html</t>
   </si>
 </sst>
 </file>
@@ -701,6 +707,9 @@
       <c r="C7" t="s">
         <v>12</v>
       </c>
+      <c r="D7" t="s">
+        <v>55</v>
+      </c>
       <c r="E7" t="s">
         <v>30</v>
       </c>
@@ -727,6 +736,9 @@
       </c>
       <c r="C9" t="s">
         <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>56</v>
       </c>
       <c r="E9" t="s">
         <v>32</v>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/Dropbox (Personal)/School/Teaching/DAV5300 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE0192D-3EDE-BF42-B04A-C7D1ECA7577B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E8064B7-18B5-814E-A2E9-C7F3087B3556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1480" yWindow="4680" windowWidth="25340" windowHeight="14540" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>Date</t>
   </si>
@@ -205,6 +205,9 @@
   </si>
   <si>
     <t>/slides/07-Inference_for_Numerical_Data.html</t>
+  </si>
+  <si>
+    <t>/slides/08-Linear_Regression.html</t>
   </si>
 </sst>
 </file>
@@ -758,6 +761,9 @@
       <c r="C10" t="s">
         <v>14</v>
       </c>
+      <c r="D10" t="s">
+        <v>57</v>
+      </c>
       <c r="E10" t="s">
         <v>33</v>
       </c>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/Dropbox (Personal)/School/Teaching/DAV5300 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E8064B7-18B5-814E-A2E9-C7F3087B3556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF78D7E-F164-1441-9340-9555C05594E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1480" yWindow="4680" windowWidth="25340" windowHeight="14540" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>Date</t>
   </si>
@@ -208,6 +208,9 @@
   </si>
   <si>
     <t>/slides/08-Linear_Regression.html</t>
+  </si>
+  <si>
+    <t>/slides/09-Logistic_Regression.html</t>
   </si>
 </sst>
 </file>
@@ -782,6 +785,9 @@
       <c r="C11" t="s">
         <v>39</v>
       </c>
+      <c r="D11" t="s">
+        <v>58</v>
+      </c>
       <c r="E11" t="s">
         <v>37</v>
       </c>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/Dropbox (Personal)/School/Teaching/DAV5300 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF78D7E-F164-1441-9340-9555C05594E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1AD8F0A-7B97-DB44-85AC-2F197FAFBCAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1480" yWindow="4680" windowWidth="25340" windowHeight="14540" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>Date</t>
   </si>
@@ -211,6 +211,9 @@
   </si>
   <si>
     <t>/slides/09-Logistic_Regression.html</t>
+  </si>
+  <si>
+    <t>/slides/09-Multiple_Regression.html</t>
   </si>
 </sst>
 </file>
@@ -806,6 +809,9 @@
       <c r="C12" t="s">
         <v>15</v>
       </c>
+      <c r="D12" t="s">
+        <v>59</v>
+      </c>
       <c r="E12" t="s">
         <v>36</v>
       </c>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/Dropbox (Personal)/School/Teaching/DAV5300 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1AD8F0A-7B97-DB44-85AC-2F197FAFBCAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3974B103-D36A-D24B-BE79-1E85E9CA5E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1480" yWindow="4680" windowWidth="25340" windowHeight="14540" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>Date</t>
   </si>
@@ -214,6 +214,9 @@
   </si>
   <si>
     <t>/slides/09-Multiple_Regression.html</t>
+  </si>
+  <si>
+    <t>/slides/09-Predictive_Modeling.html</t>
   </si>
 </sst>
 </file>
@@ -845,6 +848,9 @@
       <c r="B15" t="s">
         <v>22</v>
       </c>
+      <c r="D15" t="s">
+        <v>60</v>
+      </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/Dropbox (Personal)/School/Teaching/DAV5300 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3974B103-D36A-D24B-BE79-1E85E9CA5E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A107BE6-9239-0849-94EC-7B6E050C35E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1480" yWindow="4680" windowWidth="25340" windowHeight="14540" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>Date</t>
   </si>
@@ -217,6 +217,9 @@
   </si>
   <si>
     <t>/slides/09-Predictive_Modeling.html</t>
+  </si>
+  <si>
+    <t>/slides/10-Bayesian_and_PSA.html</t>
   </si>
 </sst>
 </file>
@@ -864,6 +867,9 @@
       <c r="C16" t="s">
         <v>16</v>
       </c>
+      <c r="D16" t="s">
+        <v>61</v>
+      </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
